--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.98820474238998</v>
+        <v>4.060583270638372</v>
       </c>
       <c r="D2" t="n">
-        <v>23.2784129582332</v>
+        <v>3.782742105712896</v>
       </c>
       <c r="E2" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F2" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.33211558481538</v>
+        <v>5.416468782532499</v>
       </c>
       <c r="D3" t="n">
-        <v>33.40185183935452</v>
+        <v>5.42780092389511</v>
       </c>
       <c r="E3" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F3" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.31949447784938</v>
+        <v>4.601917852650525</v>
       </c>
       <c r="D4" t="n">
-        <v>28.23972626458073</v>
+        <v>4.588955517994369</v>
       </c>
       <c r="E4" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F4" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.03860914687668</v>
+        <v>4.393773986367461</v>
       </c>
       <c r="D5" t="n">
-        <v>27.12120474566616</v>
+        <v>4.407195771170751</v>
       </c>
       <c r="E5" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F5" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.37196843518917</v>
+        <v>3.31044487071824</v>
       </c>
       <c r="D6" t="n">
-        <v>20.41383372125606</v>
+        <v>3.31724797970411</v>
       </c>
       <c r="E6" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F6" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.274588256155</v>
+        <v>3.294620591625188</v>
       </c>
       <c r="D7" t="n">
-        <v>20.45410025834662</v>
+        <v>3.323791291981327</v>
       </c>
       <c r="E7" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F7" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.04969914664194</v>
+        <v>3.258076111329315</v>
       </c>
       <c r="D8" t="n">
-        <v>19.92013487965494</v>
+        <v>3.237021917943927</v>
       </c>
       <c r="E8" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F8" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.2291731796101</v>
+        <v>3.124740641686641</v>
       </c>
       <c r="D9" t="n">
-        <v>19.14376020954681</v>
+        <v>3.110861034051357</v>
       </c>
       <c r="E9" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F9" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.54019221042278</v>
+        <v>3.987781234193702</v>
       </c>
       <c r="D10" t="n">
-        <v>24.59264040909208</v>
+        <v>3.996304066477464</v>
       </c>
       <c r="E10" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F10" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.23416565004032</v>
+        <v>2.313051918131553</v>
       </c>
       <c r="D11" t="n">
-        <v>14.37147901224999</v>
+        <v>2.335365339490624</v>
       </c>
       <c r="E11" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F11" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.80044104831684</v>
+        <v>4.680071670351486</v>
       </c>
       <c r="D12" t="n">
-        <v>28.79930252975483</v>
+        <v>4.679886661085161</v>
       </c>
       <c r="E12" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F12" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.3368118851781</v>
+        <v>4.279731931341442</v>
       </c>
       <c r="D13" t="n">
-        <v>26.26727470378939</v>
+        <v>4.268432139365776</v>
       </c>
       <c r="E13" t="n">
-        <v>5.045722335783928</v>
+        <v>0.8199298795648884</v>
       </c>
       <c r="F13" t="n">
-        <v>5.026566472535552</v>
+        <v>0.8168170517870272</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
